--- a/Dice_Jobs_Final.xlsx
+++ b/Dice_Jobs_Final.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,16 +427,16 @@
         <v>Easy Apply</v>
       </c>
       <c r="B2" t="str">
-        <v>N/A</v>
+        <v>US Postal Service</v>
       </c>
       <c r="C2" t="str">
-        <v>354-291</v>
+        <v>78160 - 144820</v>
       </c>
       <c r="D2" t="str">
-        <v>N/A</v>
+        <v>Atlanta, Georgia</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>2d ago</v>
       </c>
       <c r="F2" t="str">
         <v>https://www.dice.com/job-detail/51e13a7e-1e2a-475d-bda3-82172c070e1b</v>
@@ -450,16 +450,16 @@
         <v>Forensic Computer Analyst</v>
       </c>
       <c r="B3" t="str">
-        <v>N/A</v>
+        <v>US Postal Service</v>
       </c>
       <c r="C3" t="str">
-        <v>354-291</v>
+        <v>78160 - 144820</v>
       </c>
       <c r="D3" t="str">
-        <v>N/A</v>
+        <v>Atlanta, Georgia</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>2d ago</v>
       </c>
       <c r="F3" t="str">
         <v>https://www.dice.com/job-detail/51e13a7e-1e2a-475d-bda3-82172c070e1b</v>
@@ -473,16 +473,16 @@
         <v>Easy Apply</v>
       </c>
       <c r="B4" t="str">
-        <v>N/A</v>
+        <v>Infinite Computer Solutions (ICS)</v>
       </c>
       <c r="C4" t="str">
         <v>$80,000 - $90,000</v>
       </c>
       <c r="D4" t="str">
-        <v>N/A</v>
+        <v>Berkeley Heights, New Jersey</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>Yesterday</v>
       </c>
       <c r="F4" t="str">
         <v>https://www.dice.com/job-detail/68408ed2-b49c-4d41-9138-dcae74f77e65</v>
@@ -493,25 +493,25 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Certified Financial Planner, Tax Channel</v>
+        <v>Implementation Analyst (Banking Experience Required)</v>
       </c>
       <c r="B5" t="str">
-        <v>N/A</v>
+        <v>Infinite Computer Solutions (ICS)</v>
       </c>
       <c r="C5" t="str">
-        <v>00 - 110</v>
+        <v>$80,000 - $90,000</v>
       </c>
       <c r="D5" t="str">
-        <v>N/A</v>
+        <v>Berkeley Heights, New Jersey</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>Yesterday</v>
       </c>
       <c r="F5" t="str">
-        <v>https://www.dice.com/job-detail/dbbb83dd-102b-4e4e-9238-44f0885b0636</v>
+        <v>https://www.dice.com/job-detail/68408ed2-b49c-4d41-9138-dcae74f77e65</v>
       </c>
       <c r="G5" t="str">
-        <v>CFA</v>
+        <v>Analyst</v>
       </c>
     </row>
     <row r="6">
@@ -519,45 +519,45 @@
         <v>Easy Apply</v>
       </c>
       <c r="B6" t="str">
-        <v>N/A</v>
+        <v>Strategic Staffing Solutions</v>
       </c>
       <c r="C6" t="str">
-        <v>$70 - $80</v>
+        <v>USD0</v>
       </c>
       <c r="D6" t="str">
-        <v>N/A</v>
+        <v>Charlotte, North Carolina</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>Today</v>
       </c>
       <c r="F6" t="str">
-        <v>https://www.dice.com/job-detail/ee5e0eb9-0a34-4cd5-8c21-36f37e666d90</v>
+        <v>https://www.dice.com/job-detail/6af22463-0d9b-4d22-8c20-ff44c1200086</v>
       </c>
       <c r="G6" t="str">
-        <v>CFA</v>
+        <v>Analyst</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Sr. Business Analyst/Product Owner - UI/UX</v>
+        <v>Application Analyst (Python / PyFlink / Data Engineering)</v>
       </c>
       <c r="B7" t="str">
-        <v>N/A</v>
+        <v>Strategic Staffing Solutions</v>
       </c>
       <c r="C7" t="str">
-        <v>$70 - $80</v>
+        <v>USD0</v>
       </c>
       <c r="D7" t="str">
-        <v>N/A</v>
+        <v>Charlotte, North Carolina</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>Today</v>
       </c>
       <c r="F7" t="str">
-        <v>https://www.dice.com/job-detail/ee5e0eb9-0a34-4cd5-8c21-36f37e666d90</v>
+        <v>https://www.dice.com/job-detail/6af22463-0d9b-4d22-8c20-ff44c1200086</v>
       </c>
       <c r="G7" t="str">
-        <v>CFA</v>
+        <v>Analyst</v>
       </c>
     </row>
     <row r="8">
@@ -565,211 +565,487 @@
         <v>Easy Apply</v>
       </c>
       <c r="B8" t="str">
-        <v>N/A</v>
+        <v>Bright Sol</v>
       </c>
       <c r="C8" t="str">
-        <v>45-50</v>
+        <v>60 - 65</v>
       </c>
       <c r="D8" t="str">
-        <v>N/A</v>
+        <v>Sacramento, California</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>Today</v>
       </c>
       <c r="F8" t="str">
-        <v>https://www.dice.com/job-detail/a429546e-1e5e-4820-a86e-b586c5c09f37</v>
+        <v>https://www.dice.com/job-detail/6b0b7ed6-7d41-4cfe-ae2e-24756c06ff07</v>
       </c>
       <c r="G8" t="str">
-        <v>CEO</v>
+        <v>CFA</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Executive IT Services Specialist</v>
+        <v>Financial Services Manager</v>
       </c>
       <c r="B9" t="str">
-        <v>N/A</v>
+        <v>Bright Sol</v>
       </c>
       <c r="C9" t="str">
-        <v>45-50</v>
+        <v>60 - 65</v>
       </c>
       <c r="D9" t="str">
-        <v>N/A</v>
+        <v>Sacramento, California</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>Today</v>
       </c>
       <c r="F9" t="str">
-        <v>https://www.dice.com/job-detail/a429546e-1e5e-4820-a86e-b586c5c09f37</v>
+        <v>https://www.dice.com/job-detail/6b0b7ed6-7d41-4cfe-ae2e-24756c06ff07</v>
       </c>
       <c r="G9" t="str">
-        <v>CEO</v>
+        <v>CFA</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Easy Apply</v>
+        <v>Certified Financial Planner, Tax Channel</v>
       </c>
       <c r="B10" t="str">
-        <v>N/A</v>
+        <v>Cetera Financial Group, Inc.</v>
       </c>
       <c r="C10" t="str">
-        <v>$75000</v>
+        <v>USD 90</v>
       </c>
       <c r="D10" t="str">
-        <v>N/A</v>
+        <v>Dallas, Texas</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>Today</v>
       </c>
       <c r="F10" t="str">
-        <v>https://www.dice.com/job-detail/b2333592-3ab7-4ac0-ad65-17215525dd15</v>
+        <v>https://www.dice.com/job-detail/dbbb83dd-102b-4e4e-9238-44f0885b0636</v>
       </c>
       <c r="G10" t="str">
-        <v>CEO</v>
+        <v>CFA</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>IT Applications Engineer V - Data Science, Data &amp; AI Engineering, Application Engineering</v>
+        <v>Easy Apply</v>
       </c>
       <c r="B11" t="str">
-        <v>N/A</v>
+        <v>Xoriant Corporation</v>
       </c>
       <c r="C11" t="str">
-        <v>00 - 204</v>
+        <v>$70 - $80</v>
       </c>
       <c r="D11" t="str">
-        <v>N/A</v>
+        <v>Hybrid in New York, New York</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>10d ago</v>
       </c>
       <c r="F11" t="str">
-        <v>https://www.dice.com/job-detail/ffe21eeb-b255-4368-8e62-0b2896c692d3</v>
+        <v>https://www.dice.com/job-detail/ee5e0eb9-0a34-4cd5-8c21-36f37e666d90</v>
       </c>
       <c r="G11" t="str">
-        <v>Data Science</v>
+        <v>CFA</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>FLEX Manager, Data Science - Pricing Models</v>
+        <v>Sr. Business Analyst/Product Owner - UI/UX</v>
       </c>
       <c r="B12" t="str">
-        <v>N/A</v>
+        <v>Xoriant Corporation</v>
       </c>
       <c r="C12" t="str">
-        <v>73 - 51</v>
+        <v>$70 - $80</v>
       </c>
       <c r="D12" t="str">
-        <v>N/A</v>
+        <v>Hybrid in New York, New York</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>10d ago</v>
       </c>
       <c r="F12" t="str">
-        <v>https://www.dice.com/job-detail/7b3f5f72-92c5-4b09-8bfe-24b119610617</v>
+        <v>https://www.dice.com/job-detail/ee5e0eb9-0a34-4cd5-8c21-36f37e666d90</v>
       </c>
       <c r="G12" t="str">
-        <v>Data Science</v>
+        <v>CFA</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Senior Platform Engineer- Data Science</v>
+        <v>Equity Strategist</v>
       </c>
       <c r="B13" t="str">
-        <v>N/A</v>
+        <v>UBS</v>
       </c>
       <c r="C13" t="str">
-        <v>00 - 68</v>
+        <v>USD 145</v>
       </c>
       <c r="D13" t="str">
-        <v>N/A</v>
+        <v>New York, New York</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>3d ago</v>
       </c>
       <c r="F13" t="str">
-        <v>https://www.dice.com/job-detail/2ba26ebe-8e39-4bba-9266-be9c1177827f</v>
+        <v>https://www.dice.com/job-detail/b5008b16-720e-4729-a54a-2e9bbeef4ccf</v>
       </c>
       <c r="G13" t="str">
-        <v>Data Science</v>
+        <v>CFA</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Easy Apply</v>
+        <v>Hair Stylist/Barber</v>
       </c>
       <c r="B14" t="str">
-        <v>N/A</v>
+        <v>Sport Clips</v>
       </c>
       <c r="C14" t="str">
-        <v>$110000</v>
+        <v>USD 25</v>
       </c>
       <c r="D14" t="str">
-        <v>N/A</v>
+        <v>Danvers, Massachusetts</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>30+d ago</v>
       </c>
       <c r="F14" t="str">
-        <v>https://www.dice.com/job-detail/c8cbc56c-9d36-4dfc-b67f-9785ccc187b5</v>
+        <v>https://www.dice.com/job-detail/0f465078-3ac3-4862-93e5-1a229fe0c9ae</v>
       </c>
       <c r="G14" t="str">
-        <v>FP&amp;A</v>
+        <v>CEO</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SR FP&amp;A Analyst</v>
+        <v>Easy Apply</v>
       </c>
       <c r="B15" t="str">
-        <v>N/A</v>
+        <v>InfoPeople Corp</v>
       </c>
       <c r="C15" t="str">
-        <v>$110000</v>
+        <v>$140,000 - $180,000</v>
       </c>
       <c r="D15" t="str">
-        <v>N/A</v>
+        <v>Remote</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>14d ago</v>
       </c>
       <c r="F15" t="str">
-        <v>https://www.dice.com/job-detail/c8cbc56c-9d36-4dfc-b67f-9785ccc187b5</v>
+        <v>https://www.dice.com/job-detail/bded6ae6-06af-41e8-8279-f67819b5564c</v>
       </c>
       <c r="G15" t="str">
-        <v>FP&amp;A</v>
+        <v>CEO</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
+        <v>VP of Operations</v>
+      </c>
+      <c r="B16" t="str">
+        <v>InfoPeople Corp</v>
+      </c>
+      <c r="C16" t="str">
+        <v>$140,000 - $180,000</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="E16" t="str">
+        <v>14d ago</v>
+      </c>
+      <c r="F16" t="str">
+        <v>https://www.dice.com/job-detail/bded6ae6-06af-41e8-8279-f67819b5564c</v>
+      </c>
+      <c r="G16" t="str">
+        <v>CEO</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>IT Applications Engineer V - Data Science, Data &amp; AI Engineering, Application Engineering</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Kaiser Permanente</v>
+      </c>
+      <c r="C17" t="str">
+        <v>USD 158</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Pleasanton, California</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Today</v>
+      </c>
+      <c r="F17" t="str">
+        <v>https://www.dice.com/job-detail/ffe21eeb-b255-4368-8e62-0b2896c692d3</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Data Science</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Senior Platform Engineer- Data Science</v>
+      </c>
+      <c r="B18" t="str">
+        <v>TEKsystems c/o Allegis Group</v>
+      </c>
+      <c r="C18" t="str">
+        <v>USD 55</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Columbus, Ohio</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Today</v>
+      </c>
+      <c r="F18" t="str">
+        <v>https://www.dice.com/job-detail/940d7c94-7721-473d-bb71-0143fa825610</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Data Science</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Geo / Earth Data Science Internship</v>
+      </c>
+      <c r="B19" t="str">
+        <v>SAIC</v>
+      </c>
+      <c r="C19" t="str">
+        <v>026-04</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Reston, Virginia</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Today</v>
+      </c>
+      <c r="F19" t="str">
+        <v>https://www.dice.com/job-detail/34158c1c-b2b7-4dd5-96d3-2e6f5dd44cef</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Data Science</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
         <v>Easy Apply</v>
       </c>
-      <c r="B16" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="C16" t="str">
+      <c r="B20" t="str">
+        <v>Motion Recruitment Partners, LLC</v>
+      </c>
+      <c r="C20" t="str">
+        <v>$50 - $70</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Los Angeles, California</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Today</v>
+      </c>
+      <c r="F20" t="str">
+        <v>https://www.dice.com/job-detail/1201c12a-4c76-4101-8a5d-ee06514f5c84</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Data Science</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Data Science Engineer / Los Angeles / Fully Onsite / Python / LLMs / MongoDB</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Motion Recruitment Partners, LLC</v>
+      </c>
+      <c r="C21" t="str">
+        <v>$50 - $70</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Los Angeles, California</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Today</v>
+      </c>
+      <c r="F21" t="str">
+        <v>https://www.dice.com/job-detail/1201c12a-4c76-4101-8a5d-ee06514f5c84</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Data Science</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Senior Analyst, Data Science and Analytics</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Trans Union LLC</v>
+      </c>
+      <c r="C22" t="str">
+        <v>USD 67</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Chicago, Illinois</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Today</v>
+      </c>
+      <c r="F22" t="str">
+        <v>https://www.dice.com/job-detail/ac757413-35b9-44cf-a01b-d4853c1ed5f0</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Data Science</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Easy Apply</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Dexian DISYS</v>
+      </c>
+      <c r="C23" t="str">
+        <v>$110</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Tampa, Florida</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Today</v>
+      </c>
+      <c r="F23" t="str">
+        <v>https://www.dice.com/job-detail/c8cbc56c-9d36-4dfc-b67f-9785ccc187b5</v>
+      </c>
+      <c r="G23" t="str">
+        <v>FP&amp;A</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SR FP&amp;A Analyst</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Dexian DISYS</v>
+      </c>
+      <c r="C24" t="str">
+        <v>$110</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Tampa, Florida</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Today</v>
+      </c>
+      <c r="F24" t="str">
+        <v>https://www.dice.com/job-detail/c8cbc56c-9d36-4dfc-b67f-9785ccc187b5</v>
+      </c>
+      <c r="G24" t="str">
+        <v>FP&amp;A</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Easy Apply</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Nextgen Information Services</v>
+      </c>
+      <c r="C25" t="str">
         <v>$50 - $60</v>
       </c>
-      <c r="D16" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
+      <c r="D25" t="str">
+        <v>Hybrid in Des Peres, Missouri</v>
+      </c>
+      <c r="E25" t="str">
+        <v>9d ago</v>
+      </c>
+      <c r="F25" t="str">
         <v>https://www.dice.com/job-detail/42a6de77-dbb0-45be-b713-9758d2f6ec75</v>
       </c>
-      <c r="G16" t="str">
+      <c r="G25" t="str">
+        <v>FP&amp;A</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Senior Financial Analyst FP&amp;A &amp; Pricing</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Nextgen Information Services</v>
+      </c>
+      <c r="C26" t="str">
+        <v>$50 - $60</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Hybrid in Des Peres, Missouri</v>
+      </c>
+      <c r="E26" t="str">
+        <v>9d ago</v>
+      </c>
+      <c r="F26" t="str">
+        <v>https://www.dice.com/job-detail/42a6de77-dbb0-45be-b713-9758d2f6ec75</v>
+      </c>
+      <c r="G26" t="str">
+        <v>FP&amp;A</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>FP&amp;A Manager</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Judge Group, Inc.</v>
+      </c>
+      <c r="C27" t="str">
+        <v>$150,000</v>
+      </c>
+      <c r="D27" t="str">
+        <v>North Charleston, South Carolina</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Today</v>
+      </c>
+      <c r="F27" t="str">
+        <v>https://www.dice.com/job-detail/6a8561f0-d525-45be-aa81-0e4980ca3449</v>
+      </c>
+      <c r="G27" t="str">
+        <v>FP&amp;A</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Easy Apply</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Ecloud Labs</v>
+      </c>
+      <c r="C28" t="str">
+        <v>000 - 220</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Hybrid in Dallas, Texas</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Yesterday</v>
+      </c>
+      <c r="F28" t="str">
+        <v>https://www.dice.com/job-detail/04db61f5-2a44-4255-b07e-1aeaba956cb9</v>
+      </c>
+      <c r="G28" t="str">
         <v>FP&amp;A</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G28"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Dice_Jobs_Final.xlsx
+++ b/Dice_Jobs_Final.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,7 +424,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Easy Apply</v>
+        <v>Forensic Computer Analyst</v>
       </c>
       <c r="B2" t="str">
         <v>US Postal Service</v>
@@ -436,7 +436,7 @@
         <v>Atlanta, Georgia</v>
       </c>
       <c r="E2" t="str">
-        <v>2d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="F2" t="str">
         <v>https://www.dice.com/job-detail/51e13a7e-1e2a-475d-bda3-82172c070e1b</v>
@@ -447,22 +447,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Forensic Computer Analyst</v>
+        <v>Implementation Analyst (Banking Experience Required)</v>
       </c>
       <c r="B3" t="str">
-        <v>US Postal Service</v>
+        <v>Infinite Computer Solutions (ICS)</v>
       </c>
       <c r="C3" t="str">
-        <v>78160 - 144820</v>
+        <v>$80,000 - $90,000</v>
       </c>
       <c r="D3" t="str">
-        <v>Atlanta, Georgia</v>
+        <v>Berkeley Heights, New Jersey</v>
       </c>
       <c r="E3" t="str">
-        <v>2d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="F3" t="str">
-        <v>https://www.dice.com/job-detail/51e13a7e-1e2a-475d-bda3-82172c070e1b</v>
+        <v>https://www.dice.com/job-detail/68408ed2-b49c-4d41-9138-dcae74f77e65</v>
       </c>
       <c r="G3" t="str">
         <v>Analyst</v>
@@ -470,22 +470,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Easy Apply</v>
+        <v>Forensics Support Analyst</v>
       </c>
       <c r="B4" t="str">
-        <v>Infinite Computer Solutions (ICS)</v>
+        <v>Strategic Staffing Solutions</v>
       </c>
       <c r="C4" t="str">
-        <v>$80,000 - $90,000</v>
+        <v>USD30</v>
       </c>
       <c r="D4" t="str">
-        <v>Berkeley Heights, New Jersey</v>
+        <v>Houston, Texas</v>
       </c>
       <c r="E4" t="str">
-        <v>Yesterday</v>
+        <v>Today</v>
       </c>
       <c r="F4" t="str">
-        <v>https://www.dice.com/job-detail/68408ed2-b49c-4d41-9138-dcae74f77e65</v>
+        <v>https://www.dice.com/job-detail/9f2dec00-e4cb-4151-97b0-5cb8c98ec9cd</v>
       </c>
       <c r="G4" t="str">
         <v>Analyst</v>
@@ -493,22 +493,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Implementation Analyst (Banking Experience Required)</v>
+        <v>Clinical EMR Configuration Analyst</v>
       </c>
       <c r="B5" t="str">
-        <v>Infinite Computer Solutions (ICS)</v>
+        <v>NTT DATA Americas, Inc</v>
       </c>
       <c r="C5" t="str">
-        <v>$80,000 - $90,000</v>
+        <v>$50 - $60</v>
       </c>
       <c r="D5" t="str">
-        <v>Berkeley Heights, New Jersey</v>
+        <v>Franklin, Tennessee</v>
       </c>
       <c r="E5" t="str">
-        <v>Yesterday</v>
+        <v>5d ago</v>
       </c>
       <c r="F5" t="str">
-        <v>https://www.dice.com/job-detail/68408ed2-b49c-4d41-9138-dcae74f77e65</v>
+        <v>https://www.dice.com/job-detail/20ac3e66-70a3-4379-bd25-ef18b0409b2a</v>
       </c>
       <c r="G5" t="str">
         <v>Analyst</v>
@@ -516,68 +516,68 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Easy Apply</v>
+        <v>Certified Financial Planner, Tax Channel</v>
       </c>
       <c r="B6" t="str">
-        <v>Strategic Staffing Solutions</v>
+        <v>Cetera Financial Group, Inc.</v>
       </c>
       <c r="C6" t="str">
-        <v>USD0</v>
+        <v>USD 90,000.00 - 110,000.00</v>
       </c>
       <c r="D6" t="str">
-        <v>Charlotte, North Carolina</v>
+        <v>Dallas, Texas</v>
       </c>
       <c r="E6" t="str">
         <v>Today</v>
       </c>
       <c r="F6" t="str">
-        <v>https://www.dice.com/job-detail/6af22463-0d9b-4d22-8c20-ff44c1200086</v>
+        <v>https://www.dice.com/job-detail/dbbb83dd-102b-4e4e-9238-44f0885b0636</v>
       </c>
       <c r="G6" t="str">
-        <v>Analyst</v>
+        <v>CFA</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Application Analyst (Python / PyFlink / Data Engineering)</v>
+        <v>Equity Strategist</v>
       </c>
       <c r="B7" t="str">
-        <v>Strategic Staffing Solutions</v>
+        <v>UBS</v>
       </c>
       <c r="C7" t="str">
-        <v>USD0</v>
+        <v>USD 145,000.00 - 172,500.00</v>
       </c>
       <c r="D7" t="str">
-        <v>Charlotte, North Carolina</v>
+        <v>New York, New York</v>
       </c>
       <c r="E7" t="str">
-        <v>Today</v>
+        <v>2d ago</v>
       </c>
       <c r="F7" t="str">
-        <v>https://www.dice.com/job-detail/6af22463-0d9b-4d22-8c20-ff44c1200086</v>
+        <v>https://www.dice.com/job-detail/b5008b16-720e-4729-a54a-2e9bbeef4ccf</v>
       </c>
       <c r="G7" t="str">
-        <v>Analyst</v>
+        <v>CFA</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Easy Apply</v>
+        <v>Director of FP&amp;A</v>
       </c>
       <c r="B8" t="str">
-        <v>Bright Sol</v>
+        <v>HAYS</v>
       </c>
       <c r="C8" t="str">
-        <v>60 - 65</v>
+        <v>USD 150,000.00 - 160,000.00</v>
       </c>
       <c r="D8" t="str">
-        <v>Sacramento, California</v>
+        <v>Florida</v>
       </c>
       <c r="E8" t="str">
         <v>Today</v>
       </c>
       <c r="F8" t="str">
-        <v>https://www.dice.com/job-detail/6b0b7ed6-7d41-4cfe-ae2e-24756c06ff07</v>
+        <v>https://www.dice.com/job-detail/873bfad6-3437-40e4-9c31-5a2c63551ef6</v>
       </c>
       <c r="G8" t="str">
         <v>CFA</v>
@@ -585,206 +585,206 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Financial Services Manager</v>
+        <v>VP of Operations / Integrator</v>
       </c>
       <c r="B9" t="str">
-        <v>Bright Sol</v>
+        <v>SherlockTalent</v>
       </c>
       <c r="C9" t="str">
-        <v>60 - 65</v>
+        <v>$225,000</v>
       </c>
       <c r="D9" t="str">
-        <v>Sacramento, California</v>
+        <v>Hybrid in Aventura, Florida</v>
       </c>
       <c r="E9" t="str">
-        <v>Today</v>
+        <v>5d ago</v>
       </c>
       <c r="F9" t="str">
-        <v>https://www.dice.com/job-detail/6b0b7ed6-7d41-4cfe-ae2e-24756c06ff07</v>
+        <v>https://www.dice.com/job-detail/e22d7802-2044-4b53-96d7-a9dcfc660876</v>
       </c>
       <c r="G9" t="str">
-        <v>CFA</v>
+        <v>CEO</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Certified Financial Planner, Tax Channel</v>
+        <v>Senior Platform Engineer- Data Science</v>
       </c>
       <c r="B10" t="str">
-        <v>Cetera Financial Group, Inc.</v>
+        <v>TEKsystems c/o Allegis Group</v>
       </c>
       <c r="C10" t="str">
-        <v>USD 90</v>
+        <v>USD 55.00 - 68.00</v>
       </c>
       <c r="D10" t="str">
-        <v>Dallas, Texas</v>
+        <v>Columbus, Ohio</v>
       </c>
       <c r="E10" t="str">
         <v>Today</v>
       </c>
       <c r="F10" t="str">
-        <v>https://www.dice.com/job-detail/dbbb83dd-102b-4e4e-9238-44f0885b0636</v>
+        <v>https://www.dice.com/job-detail/7c560ded-a9ff-4938-a6a9-c19a531a9217</v>
       </c>
       <c r="G10" t="str">
-        <v>CFA</v>
+        <v>Data Science</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Easy Apply</v>
+        <v>Data Science Senior Analyst</v>
       </c>
       <c r="B11" t="str">
-        <v>Xoriant Corporation</v>
+        <v>Advantage Technical</v>
       </c>
       <c r="C11" t="str">
-        <v>$70 - $80</v>
+        <v>USD 40.88</v>
       </c>
       <c r="D11" t="str">
-        <v>Hybrid in New York, New York</v>
+        <v>Round Rock, Texas</v>
       </c>
       <c r="E11" t="str">
-        <v>10d ago</v>
+        <v>Today</v>
       </c>
       <c r="F11" t="str">
-        <v>https://www.dice.com/job-detail/ee5e0eb9-0a34-4cd5-8c21-36f37e666d90</v>
+        <v>https://www.dice.com/job-detail/7a0b62ae-de62-4c5b-8862-6c0caae232ad</v>
       </c>
       <c r="G11" t="str">
-        <v>CFA</v>
+        <v>Data Science</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Sr. Business Analyst/Product Owner - UI/UX</v>
+        <v>Senior Analyst, Data Science and Analytics</v>
       </c>
       <c r="B12" t="str">
-        <v>Xoriant Corporation</v>
+        <v>Trans Union LLC</v>
       </c>
       <c r="C12" t="str">
-        <v>$70 - $80</v>
+        <v>USD 67,500.00 - 112,500.00</v>
       </c>
       <c r="D12" t="str">
-        <v>Hybrid in New York, New York</v>
+        <v>Chicago, Illinois</v>
       </c>
       <c r="E12" t="str">
-        <v>10d ago</v>
+        <v>Today</v>
       </c>
       <c r="F12" t="str">
-        <v>https://www.dice.com/job-detail/ee5e0eb9-0a34-4cd5-8c21-36f37e666d90</v>
+        <v>https://www.dice.com/job-detail/ac757413-35b9-44cf-a01b-d4853c1ed5f0</v>
       </c>
       <c r="G12" t="str">
-        <v>CFA</v>
+        <v>Data Science</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Equity Strategist</v>
+        <v>Data Science Analyst -- Part of B&amp;B do not work</v>
       </c>
       <c r="B13" t="str">
-        <v>UBS</v>
+        <v>Apex Systems</v>
       </c>
       <c r="C13" t="str">
-        <v>USD 145</v>
+        <v>USD 67.81 - 72.33</v>
       </c>
       <c r="D13" t="str">
-        <v>New York, New York</v>
+        <v>Charlotte, North Carolina</v>
       </c>
       <c r="E13" t="str">
-        <v>3d ago</v>
+        <v>Today</v>
       </c>
       <c r="F13" t="str">
-        <v>https://www.dice.com/job-detail/b5008b16-720e-4729-a54a-2e9bbeef4ccf</v>
+        <v>https://www.dice.com/job-detail/e40ad386-88c7-49f7-958e-7aa8797a1f8b</v>
       </c>
       <c r="G13" t="str">
-        <v>CFA</v>
+        <v>Data Science</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Hair Stylist/Barber</v>
+        <v>Senior Manager of Data Science</v>
       </c>
       <c r="B14" t="str">
-        <v>Sport Clips</v>
+        <v>Kforce Technology Staffing</v>
       </c>
       <c r="C14" t="str">
-        <v>USD 25</v>
+        <v>$180,000 - $200,000</v>
       </c>
       <c r="D14" t="str">
-        <v>Danvers, Massachusetts</v>
+        <v>Louisville, Kentucky</v>
       </c>
       <c r="E14" t="str">
-        <v>30+d ago</v>
+        <v>Today</v>
       </c>
       <c r="F14" t="str">
-        <v>https://www.dice.com/job-detail/0f465078-3ac3-4862-93e5-1a229fe0c9ae</v>
+        <v>https://www.dice.com/job-detail/50935afb-6ec9-4df1-956b-0c24e0301e0f</v>
       </c>
       <c r="G14" t="str">
-        <v>CEO</v>
+        <v>Data Science</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Easy Apply</v>
+        <v>AI / Data Science Engineer / Remote / Work-Life Balance</v>
       </c>
       <c r="B15" t="str">
-        <v>InfoPeople Corp</v>
+        <v>Motion Recruitment Partners, LLC</v>
       </c>
       <c r="C15" t="str">
-        <v>$140,000 - $180,000</v>
+        <v>$40 - $60</v>
       </c>
       <c r="D15" t="str">
         <v>Remote</v>
       </c>
       <c r="E15" t="str">
-        <v>14d ago</v>
+        <v>Today</v>
       </c>
       <c r="F15" t="str">
-        <v>https://www.dice.com/job-detail/bded6ae6-06af-41e8-8279-f67819b5564c</v>
+        <v>https://www.dice.com/job-detail/9a7a7f67-9c45-49f6-96ab-65fe97db6811</v>
       </c>
       <c r="G15" t="str">
-        <v>CEO</v>
+        <v>Data Science</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>VP of Operations</v>
+        <v>Technical Program Manager - Marketing Data Science</v>
       </c>
       <c r="B16" t="str">
-        <v>InfoPeople Corp</v>
+        <v>Tandym Tech</v>
       </c>
       <c r="C16" t="str">
-        <v>$140,000 - $180,000</v>
+        <v>$65 - $70</v>
       </c>
       <c r="D16" t="str">
-        <v>Remote</v>
+        <v>Vienna, Virginia</v>
       </c>
       <c r="E16" t="str">
-        <v>14d ago</v>
+        <v>Today</v>
       </c>
       <c r="F16" t="str">
-        <v>https://www.dice.com/job-detail/bded6ae6-06af-41e8-8279-f67819b5564c</v>
+        <v>https://www.dice.com/job-detail/880db6de-9ee5-4a3d-a440-ea94fa905c0e</v>
       </c>
       <c r="G16" t="str">
-        <v>CEO</v>
+        <v>Data Science</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>IT Applications Engineer V - Data Science, Data &amp; AI Engineering, Application Engineering</v>
+        <v>Senior Director, Data Science Product Development, Specialized Risk</v>
       </c>
       <c r="B17" t="str">
-        <v>Kaiser Permanente</v>
+        <v>Trans Union LLC</v>
       </c>
       <c r="C17" t="str">
-        <v>USD 158</v>
+        <v>USD 166,800.00 - 250,000.00</v>
       </c>
       <c r="D17" t="str">
-        <v>Pleasanton, California</v>
+        <v>New York, New York</v>
       </c>
       <c r="E17" t="str">
         <v>Today</v>
       </c>
       <c r="F17" t="str">
-        <v>https://www.dice.com/job-detail/ffe21eeb-b255-4368-8e62-0b2896c692d3</v>
+        <v>https://www.dice.com/job-detail/1a3d9e02-ee12-413d-b326-9535e4acb9f0</v>
       </c>
       <c r="G17" t="str">
         <v>Data Science</v>
@@ -792,22 +792,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Senior Platform Engineer- Data Science</v>
+        <v>Senior Director, Data Science Product Development, Specialized Risk</v>
       </c>
       <c r="B18" t="str">
-        <v>TEKsystems c/o Allegis Group</v>
+        <v>Trans Union LLC</v>
       </c>
       <c r="C18" t="str">
-        <v>USD 55</v>
+        <v>USD 166,800.00 - 250,000.00</v>
       </c>
       <c r="D18" t="str">
-        <v>Columbus, Ohio</v>
+        <v>Pennsylvania</v>
       </c>
       <c r="E18" t="str">
         <v>Today</v>
       </c>
       <c r="F18" t="str">
-        <v>https://www.dice.com/job-detail/940d7c94-7721-473d-bb71-0143fa825610</v>
+        <v>https://www.dice.com/job-detail/bb1f8c88-001f-4078-a08a-c548c76b2d8f</v>
       </c>
       <c r="G18" t="str">
         <v>Data Science</v>
@@ -815,22 +815,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Geo / Earth Data Science Internship</v>
+        <v>Senior Director, Data Science Product Development, Specialized Risk</v>
       </c>
       <c r="B19" t="str">
-        <v>SAIC</v>
+        <v>Trans Union LLC</v>
       </c>
       <c r="C19" t="str">
-        <v>026-04</v>
+        <v>USD 166,800.00 - 250,000.00</v>
       </c>
       <c r="D19" t="str">
-        <v>Reston, Virginia</v>
+        <v>Greenwood Village, Colorado</v>
       </c>
       <c r="E19" t="str">
         <v>Today</v>
       </c>
       <c r="F19" t="str">
-        <v>https://www.dice.com/job-detail/34158c1c-b2b7-4dd5-96d3-2e6f5dd44cef</v>
+        <v>https://www.dice.com/job-detail/7b22c851-2330-4460-bcd0-bc4c4c6b638f</v>
       </c>
       <c r="G19" t="str">
         <v>Data Science</v>
@@ -838,22 +838,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Easy Apply</v>
+        <v>Senior Director, Data Science Product Development, Specialized Risk</v>
       </c>
       <c r="B20" t="str">
-        <v>Motion Recruitment Partners, LLC</v>
+        <v>Trans Union LLC</v>
       </c>
       <c r="C20" t="str">
-        <v>$50 - $70</v>
+        <v>USD 166,800.00 - 250,000.00</v>
       </c>
       <c r="D20" t="str">
-        <v>Los Angeles, California</v>
+        <v>White Plains, New York</v>
       </c>
       <c r="E20" t="str">
         <v>Today</v>
       </c>
       <c r="F20" t="str">
-        <v>https://www.dice.com/job-detail/1201c12a-4c76-4101-8a5d-ee06514f5c84</v>
+        <v>https://www.dice.com/job-detail/68663728-18e1-4d44-9c74-51b3aa900b2b</v>
       </c>
       <c r="G20" t="str">
         <v>Data Science</v>
@@ -861,22 +861,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Data Science Engineer / Los Angeles / Fully Onsite / Python / LLMs / MongoDB</v>
+        <v>Senior Director, Data Science Product Development, Specialized Risk</v>
       </c>
       <c r="B21" t="str">
-        <v>Motion Recruitment Partners, LLC</v>
+        <v>Trans Union LLC</v>
       </c>
       <c r="C21" t="str">
-        <v>$50 - $70</v>
+        <v>USD 166,800.00 - 250,000.00</v>
       </c>
       <c r="D21" t="str">
-        <v>Los Angeles, California</v>
+        <v>Boca Raton, Florida</v>
       </c>
       <c r="E21" t="str">
         <v>Today</v>
       </c>
       <c r="F21" t="str">
-        <v>https://www.dice.com/job-detail/1201c12a-4c76-4101-8a5d-ee06514f5c84</v>
+        <v>https://www.dice.com/job-detail/99d58368-6f96-4729-aa0f-389e4c851d19</v>
       </c>
       <c r="G21" t="str">
         <v>Data Science</v>
@@ -884,45 +884,45 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Senior Analyst, Data Science and Analytics</v>
+        <v>SR FP&amp;A Analyst</v>
       </c>
       <c r="B22" t="str">
-        <v>Trans Union LLC</v>
+        <v>Dexian DISYS</v>
       </c>
       <c r="C22" t="str">
-        <v>USD 67</v>
+        <v>$110</v>
       </c>
       <c r="D22" t="str">
-        <v>Chicago, Illinois</v>
+        <v>Tampa, Florida</v>
       </c>
       <c r="E22" t="str">
         <v>Today</v>
       </c>
       <c r="F22" t="str">
-        <v>https://www.dice.com/job-detail/ac757413-35b9-44cf-a01b-d4853c1ed5f0</v>
+        <v>https://www.dice.com/job-detail/c8cbc56c-9d36-4dfc-b67f-9785ccc187b5</v>
       </c>
       <c r="G22" t="str">
-        <v>Data Science</v>
+        <v>FP&amp;A</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Easy Apply</v>
+        <v>FP&amp;A Manager</v>
       </c>
       <c r="B23" t="str">
-        <v>Dexian DISYS</v>
+        <v>Judge Group, Inc.</v>
       </c>
       <c r="C23" t="str">
-        <v>$110</v>
+        <v>$150,000</v>
       </c>
       <c r="D23" t="str">
-        <v>Tampa, Florida</v>
+        <v>North Charleston, South Carolina</v>
       </c>
       <c r="E23" t="str">
         <v>Today</v>
       </c>
       <c r="F23" t="str">
-        <v>https://www.dice.com/job-detail/c8cbc56c-9d36-4dfc-b67f-9785ccc187b5</v>
+        <v>https://www.dice.com/job-detail/6a8561f0-d525-45be-aa81-0e4980ca3449</v>
       </c>
       <c r="G23" t="str">
         <v>FP&amp;A</v>
@@ -930,22 +930,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SR FP&amp;A Analyst</v>
+        <v>FP&amp;A Director - McKesson Technology</v>
       </c>
       <c r="B24" t="str">
-        <v>Dexian DISYS</v>
+        <v>McKesson Corporation</v>
       </c>
       <c r="C24" t="str">
-        <v>$110</v>
+        <v>USD 135,800.00 - 226,400.00</v>
       </c>
       <c r="D24" t="str">
-        <v>Tampa, Florida</v>
+        <v>Remote or Irving, Texas</v>
       </c>
       <c r="E24" t="str">
         <v>Today</v>
       </c>
       <c r="F24" t="str">
-        <v>https://www.dice.com/job-detail/c8cbc56c-9d36-4dfc-b67f-9785ccc187b5</v>
+        <v>https://www.dice.com/job-detail/91d51739-dc79-41f4-80f4-411bb3d5d5b4</v>
       </c>
       <c r="G24" t="str">
         <v>FP&amp;A</v>
@@ -953,22 +953,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Easy Apply</v>
+        <v>Senior FP&amp;A Analyst - Technical Infrastructure</v>
       </c>
       <c r="B25" t="str">
-        <v>Nextgen Information Services</v>
+        <v>Waymo</v>
       </c>
       <c r="C25" t="str">
-        <v>$50 - $60</v>
+        <v>USD 168,000.00 - 207,000.00</v>
       </c>
       <c r="D25" t="str">
-        <v>Hybrid in Des Peres, Missouri</v>
+        <v>Mountain View, California</v>
       </c>
       <c r="E25" t="str">
-        <v>9d ago</v>
+        <v>Today</v>
       </c>
       <c r="F25" t="str">
-        <v>https://www.dice.com/job-detail/42a6de77-dbb0-45be-b713-9758d2f6ec75</v>
+        <v>https://www.dice.com/job-detail/d759580f-5cb2-47fe-9fc7-1dabc1065639</v>
       </c>
       <c r="G25" t="str">
         <v>FP&amp;A</v>
@@ -976,22 +976,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Senior Financial Analyst FP&amp;A &amp; Pricing</v>
+        <v>FP&amp;A Analyst</v>
       </c>
       <c r="B26" t="str">
-        <v>Nextgen Information Services</v>
+        <v>Two Sigma Investments, LLC.</v>
       </c>
       <c r="C26" t="str">
-        <v>$50 - $60</v>
+        <v>USD 100,000.00 - 150,000.00</v>
       </c>
       <c r="D26" t="str">
-        <v>Hybrid in Des Peres, Missouri</v>
+        <v>New York, New York</v>
       </c>
       <c r="E26" t="str">
-        <v>9d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="F26" t="str">
-        <v>https://www.dice.com/job-detail/42a6de77-dbb0-45be-b713-9758d2f6ec75</v>
+        <v>https://www.dice.com/job-detail/e381eac2-5e71-4f1c-a14a-c02debed842f</v>
       </c>
       <c r="G26" t="str">
         <v>FP&amp;A</v>
@@ -999,22 +999,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>FP&amp;A Manager</v>
+        <v>FP&amp;A Data Engineer</v>
       </c>
       <c r="B27" t="str">
-        <v>Judge Group, Inc.</v>
+        <v>Galaxy</v>
       </c>
       <c r="C27" t="str">
-        <v>$150,000</v>
+        <v>USD 175,000.00 - 200,000.00</v>
       </c>
       <c r="D27" t="str">
-        <v>North Charleston, South Carolina</v>
+        <v>New York, New York</v>
       </c>
       <c r="E27" t="str">
-        <v>Today</v>
+        <v>4d ago</v>
       </c>
       <c r="F27" t="str">
-        <v>https://www.dice.com/job-detail/6a8561f0-d525-45be-aa81-0e4980ca3449</v>
+        <v>https://www.dice.com/job-detail/5aef83cd-6436-4fd9-920a-7b8dca72a25f</v>
       </c>
       <c r="G27" t="str">
         <v>FP&amp;A</v>
@@ -1022,30 +1022,53 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Easy Apply</v>
+        <v>Sr Data Analyst - FP&amp;A Reporting &amp; Analytics</v>
       </c>
       <c r="B28" t="str">
-        <v>Ecloud Labs</v>
+        <v>Target Corporation</v>
       </c>
       <c r="C28" t="str">
-        <v>000 - 220</v>
+        <v>$88,000</v>
       </c>
       <c r="D28" t="str">
-        <v>Hybrid in Dallas, Texas</v>
+        <v>Remote or Minneapolis, Minnesota</v>
       </c>
       <c r="E28" t="str">
-        <v>Yesterday</v>
+        <v>Today</v>
       </c>
       <c r="F28" t="str">
-        <v>https://www.dice.com/job-detail/04db61f5-2a44-4255-b07e-1aeaba956cb9</v>
+        <v>https://www.dice.com/job-detail/bf0d9301-c4d4-4f8b-9596-8e997c8cf0fe</v>
       </c>
       <c r="G28" t="str">
         <v>FP&amp;A</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>SeniorFinanceAnalyst</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Infinite Computer Solutions (ICS)</v>
+      </c>
+      <c r="C29" t="str">
+        <v>$100,000 - $140,000</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Hybrid in Rockville, Maryland</v>
+      </c>
+      <c r="E29" t="str">
+        <v>9d ago</v>
+      </c>
+      <c r="F29" t="str">
+        <v>https://www.dice.com/job-detail/49f3864c-3b4b-4014-b1e7-7886e5b57c0e</v>
+      </c>
+      <c r="G29" t="str">
+        <v>FP&amp;A</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G29"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Dice_Jobs_Final.xlsx
+++ b/Dice_Jobs_Final.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G35"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,7 +436,7 @@
         <v>Atlanta, Georgia</v>
       </c>
       <c r="E2" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="F2" t="str">
         <v>https://www.dice.com/job-detail/51e13a7e-1e2a-475d-bda3-82172c070e1b</v>
@@ -459,7 +459,7 @@
         <v>Berkeley Heights, New Jersey</v>
       </c>
       <c r="E3" t="str">
-        <v>7d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="F3" t="str">
         <v>https://www.dice.com/job-detail/68408ed2-b49c-4d41-9138-dcae74f77e65</v>
@@ -505,7 +505,7 @@
         <v>Franklin, Tennessee</v>
       </c>
       <c r="E5" t="str">
-        <v>5d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="F5" t="str">
         <v>https://www.dice.com/job-detail/20ac3e66-70a3-4379-bd25-ef18b0409b2a</v>
@@ -516,22 +516,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Certified Financial Planner, Tax Channel</v>
+        <v>Business Analyst (Loan IQ and data modeling)</v>
       </c>
       <c r="B6" t="str">
-        <v>Cetera Financial Group, Inc.</v>
+        <v>VeridianTech</v>
       </c>
       <c r="C6" t="str">
-        <v>USD 90,000.00 - 110,000.00</v>
+        <v>$60 - $65</v>
       </c>
       <c r="D6" t="str">
-        <v>Dallas, Texas</v>
+        <v>Woodbridge Township, New Jersey</v>
       </c>
       <c r="E6" t="str">
         <v>Today</v>
       </c>
       <c r="F6" t="str">
-        <v>https://www.dice.com/job-detail/dbbb83dd-102b-4e4e-9238-44f0885b0636</v>
+        <v>https://www.dice.com/job-detail/eafcc170-e351-4789-88d7-bd2454a0565a</v>
       </c>
       <c r="G6" t="str">
         <v>CFA</v>
@@ -539,22 +539,22 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Equity Strategist</v>
+        <v>Certified Financial Planner, Tax Channel</v>
       </c>
       <c r="B7" t="str">
-        <v>UBS</v>
+        <v>Cetera Financial Group, Inc.</v>
       </c>
       <c r="C7" t="str">
-        <v>USD 145,000.00 - 172,500.00</v>
+        <v>USD 90,000.00 - 110,000.00</v>
       </c>
       <c r="D7" t="str">
-        <v>New York, New York</v>
+        <v>Dallas, Texas</v>
       </c>
       <c r="E7" t="str">
-        <v>2d ago</v>
+        <v>Today</v>
       </c>
       <c r="F7" t="str">
-        <v>https://www.dice.com/job-detail/b5008b16-720e-4729-a54a-2e9bbeef4ccf</v>
+        <v>https://www.dice.com/job-detail/dbbb83dd-102b-4e4e-9238-44f0885b0636</v>
       </c>
       <c r="G7" t="str">
         <v>CFA</v>
@@ -562,22 +562,22 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Director of FP&amp;A</v>
+        <v>Equity Strategist</v>
       </c>
       <c r="B8" t="str">
-        <v>HAYS</v>
+        <v>UBS</v>
       </c>
       <c r="C8" t="str">
-        <v>USD 150,000.00 - 160,000.00</v>
+        <v>USD 145,000.00 - 172,500.00</v>
       </c>
       <c r="D8" t="str">
-        <v>Florida</v>
+        <v>New York, New York</v>
       </c>
       <c r="E8" t="str">
-        <v>Today</v>
+        <v>3d ago</v>
       </c>
       <c r="F8" t="str">
-        <v>https://www.dice.com/job-detail/873bfad6-3437-40e4-9c31-5a2c63551ef6</v>
+        <v>https://www.dice.com/job-detail/b5008b16-720e-4729-a54a-2e9bbeef4ccf</v>
       </c>
       <c r="G8" t="str">
         <v>CFA</v>
@@ -585,183 +585,183 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>VP of Operations / Integrator</v>
+        <v>Director of FP&amp;A</v>
       </c>
       <c r="B9" t="str">
-        <v>SherlockTalent</v>
+        <v>HAYS</v>
       </c>
       <c r="C9" t="str">
-        <v>$225,000</v>
+        <v>USD 150,000.00 - 160,000.00</v>
       </c>
       <c r="D9" t="str">
-        <v>Hybrid in Aventura, Florida</v>
+        <v>Florida</v>
       </c>
       <c r="E9" t="str">
-        <v>5d ago</v>
+        <v>Today</v>
       </c>
       <c r="F9" t="str">
-        <v>https://www.dice.com/job-detail/e22d7802-2044-4b53-96d7-a9dcfc660876</v>
+        <v>https://www.dice.com/job-detail/873bfad6-3437-40e4-9c31-5a2c63551ef6</v>
       </c>
       <c r="G9" t="str">
-        <v>CEO</v>
+        <v>CFA</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Senior Platform Engineer- Data Science</v>
+        <v>Healthcare Investment Consultant</v>
       </c>
       <c r="B10" t="str">
-        <v>TEKsystems c/o Allegis Group</v>
+        <v>Marsh McLennan</v>
       </c>
       <c r="C10" t="str">
-        <v>USD 55.00 - 68.00</v>
+        <v>USD 122,400.00 - 244,800.00</v>
       </c>
       <c r="D10" t="str">
-        <v>Columbus, Ohio</v>
+        <v>Chicago, Illinois</v>
       </c>
       <c r="E10" t="str">
-        <v>Today</v>
+        <v>3d ago</v>
       </c>
       <c r="F10" t="str">
-        <v>https://www.dice.com/job-detail/7c560ded-a9ff-4938-a6a9-c19a531a9217</v>
+        <v>https://www.dice.com/job-detail/2c544302-28fb-4cf3-b7aa-e8e9a288a562</v>
       </c>
       <c r="G10" t="str">
-        <v>Data Science</v>
+        <v>CFA</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Data Science Senior Analyst</v>
+        <v>Senior Consultant, Trade Performance &amp; Analytics</v>
       </c>
       <c r="B11" t="str">
-        <v>Advantage Technical</v>
+        <v>Northern Trust</v>
       </c>
       <c r="C11" t="str">
-        <v>USD 40.88</v>
+        <v>USD 83,100.00 - 141,300.00</v>
       </c>
       <c r="D11" t="str">
-        <v>Round Rock, Texas</v>
+        <v>Chicago, Illinois</v>
       </c>
       <c r="E11" t="str">
-        <v>Today</v>
+        <v>Yesterday</v>
       </c>
       <c r="F11" t="str">
-        <v>https://www.dice.com/job-detail/7a0b62ae-de62-4c5b-8862-6c0caae232ad</v>
+        <v>https://www.dice.com/job-detail/cc231a0c-ad57-4c9b-8a57-a3b8db80e183</v>
       </c>
       <c r="G11" t="str">
-        <v>Data Science</v>
+        <v>CFA</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Senior Analyst, Data Science and Analytics</v>
+        <v>Healthcare Senior Investment Consultant</v>
       </c>
       <c r="B12" t="str">
-        <v>Trans Union LLC</v>
+        <v>Marsh McLennan</v>
       </c>
       <c r="C12" t="str">
-        <v>USD 67,500.00 - 112,500.00</v>
+        <v>USD 162,000.00 - 324,000.00</v>
       </c>
       <c r="D12" t="str">
         <v>Chicago, Illinois</v>
       </c>
       <c r="E12" t="str">
-        <v>Today</v>
+        <v>5d ago</v>
       </c>
       <c r="F12" t="str">
-        <v>https://www.dice.com/job-detail/ac757413-35b9-44cf-a01b-d4853c1ed5f0</v>
+        <v>https://www.dice.com/job-detail/712d5b61-a38d-4b98-ba4e-a4e4ba9eda84</v>
       </c>
       <c r="G12" t="str">
-        <v>Data Science</v>
+        <v>CFA</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Data Science Analyst -- Part of B&amp;B do not work</v>
+        <v>Manufacturing Engineer</v>
       </c>
       <c r="B13" t="str">
-        <v>Apex Systems</v>
+        <v>Jobot</v>
       </c>
       <c r="C13" t="str">
-        <v>USD 67.81 - 72.33</v>
+        <v>$80,000 - $110,000</v>
       </c>
       <c r="D13" t="str">
-        <v>Charlotte, North Carolina</v>
+        <v>Bristol, Virginia</v>
       </c>
       <c r="E13" t="str">
         <v>Today</v>
       </c>
       <c r="F13" t="str">
-        <v>https://www.dice.com/job-detail/e40ad386-88c7-49f7-958e-7aa8797a1f8b</v>
+        <v>https://www.dice.com/job-detail/2839101a-1212-43fe-9f7a-d1bf48623fba</v>
       </c>
       <c r="G13" t="str">
-        <v>Data Science</v>
+        <v>CEO</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Senior Manager of Data Science</v>
+        <v>VP of Operations / Integrator</v>
       </c>
       <c r="B14" t="str">
-        <v>Kforce Technology Staffing</v>
+        <v>SherlockTalent</v>
       </c>
       <c r="C14" t="str">
-        <v>$180,000 - $200,000</v>
+        <v>$225,000</v>
       </c>
       <c r="D14" t="str">
-        <v>Louisville, Kentucky</v>
+        <v>Hybrid in Aventura, Florida</v>
       </c>
       <c r="E14" t="str">
-        <v>Today</v>
+        <v>6d ago</v>
       </c>
       <c r="F14" t="str">
-        <v>https://www.dice.com/job-detail/50935afb-6ec9-4df1-956b-0c24e0301e0f</v>
+        <v>https://www.dice.com/job-detail/e22d7802-2044-4b53-96d7-a9dcfc660876</v>
       </c>
       <c r="G14" t="str">
-        <v>Data Science</v>
+        <v>CEO</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>AI / Data Science Engineer / Remote / Work-Life Balance</v>
+        <v>AI Implementation Engineer</v>
       </c>
       <c r="B15" t="str">
-        <v>Motion Recruitment Partners, LLC</v>
+        <v>Kforce Technology Staffing</v>
       </c>
       <c r="C15" t="str">
-        <v>$40 - $60</v>
+        <v>$35 - $50</v>
       </c>
       <c r="D15" t="str">
-        <v>Remote</v>
+        <v>Coral Gables, Florida</v>
       </c>
       <c r="E15" t="str">
         <v>Today</v>
       </c>
       <c r="F15" t="str">
-        <v>https://www.dice.com/job-detail/9a7a7f67-9c45-49f6-96ab-65fe97db6811</v>
+        <v>https://www.dice.com/job-detail/1085bc48-59d6-4a0c-93c7-deb67bec1632</v>
       </c>
       <c r="G15" t="str">
-        <v>Data Science</v>
+        <v>CEO</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Technical Program Manager - Marketing Data Science</v>
+        <v>Data Science / Machine Learning Austin, TX / Raleigh, NC (Hybrid 3 Days Onsite) only on w2 USC</v>
       </c>
       <c r="B16" t="str">
-        <v>Tandym Tech</v>
+        <v>BURGEON IT SERVICES LLC</v>
       </c>
       <c r="C16" t="str">
-        <v>$65 - $70</v>
+        <v>$60 - $70</v>
       </c>
       <c r="D16" t="str">
-        <v>Vienna, Virginia</v>
+        <v>Hybrid in Austin, Texas</v>
       </c>
       <c r="E16" t="str">
         <v>Today</v>
       </c>
       <c r="F16" t="str">
-        <v>https://www.dice.com/job-detail/880db6de-9ee5-4a3d-a440-ea94fa905c0e</v>
+        <v>https://www.dice.com/job-detail/442354cc-541b-47cd-a3b7-270d9c52ab68</v>
       </c>
       <c r="G16" t="str">
         <v>Data Science</v>
@@ -769,22 +769,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Senior Director, Data Science Product Development, Specialized Risk</v>
+        <v>Principal Data Scientist (Card Decision Science)</v>
       </c>
       <c r="B17" t="str">
-        <v>Trans Union LLC</v>
+        <v>Navy Federal Credit Union</v>
       </c>
       <c r="C17" t="str">
-        <v>USD 166,800.00 - 250,000.00</v>
+        <v>$130,500-$179,500</v>
       </c>
       <c r="D17" t="str">
-        <v>New York, New York</v>
+        <v>Hybrid in Vienna, Virginia</v>
       </c>
       <c r="E17" t="str">
         <v>Today</v>
       </c>
       <c r="F17" t="str">
-        <v>https://www.dice.com/job-detail/1a3d9e02-ee12-413d-b326-9535e4acb9f0</v>
+        <v>https://www.dice.com/job-detail/343a57a4-619a-4459-a0d7-8baca0145242</v>
       </c>
       <c r="G17" t="str">
         <v>Data Science</v>
@@ -792,22 +792,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Senior Director, Data Science Product Development, Specialized Risk</v>
+        <v>Senior Platform Engineer- Data Science</v>
       </c>
       <c r="B18" t="str">
-        <v>Trans Union LLC</v>
+        <v>TEKsystems c/o Allegis Group</v>
       </c>
       <c r="C18" t="str">
-        <v>USD 166,800.00 - 250,000.00</v>
+        <v>USD 55.00 - 68.00</v>
       </c>
       <c r="D18" t="str">
-        <v>Pennsylvania</v>
+        <v>Columbus, Ohio</v>
       </c>
       <c r="E18" t="str">
         <v>Today</v>
       </c>
       <c r="F18" t="str">
-        <v>https://www.dice.com/job-detail/bb1f8c88-001f-4078-a08a-c548c76b2d8f</v>
+        <v>https://www.dice.com/job-detail/7c560ded-a9ff-4938-a6a9-c19a531a9217</v>
       </c>
       <c r="G18" t="str">
         <v>Data Science</v>
@@ -815,22 +815,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Senior Director, Data Science Product Development, Specialized Risk</v>
+        <v>Senior Analyst, Data Science and Analytics</v>
       </c>
       <c r="B19" t="str">
         <v>Trans Union LLC</v>
       </c>
       <c r="C19" t="str">
-        <v>USD 166,800.00 - 250,000.00</v>
+        <v>USD 67,500.00 - 112,500.00</v>
       </c>
       <c r="D19" t="str">
-        <v>Greenwood Village, Colorado</v>
+        <v>Chicago, Illinois</v>
       </c>
       <c r="E19" t="str">
         <v>Today</v>
       </c>
       <c r="F19" t="str">
-        <v>https://www.dice.com/job-detail/7b22c851-2330-4460-bcd0-bc4c4c6b638f</v>
+        <v>https://www.dice.com/job-detail/ac757413-35b9-44cf-a01b-d4853c1ed5f0</v>
       </c>
       <c r="G19" t="str">
         <v>Data Science</v>
@@ -838,22 +838,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Senior Director, Data Science Product Development, Specialized Risk</v>
+        <v>Data Science Analyst -- Part of B&amp;B do not work</v>
       </c>
       <c r="B20" t="str">
-        <v>Trans Union LLC</v>
+        <v>Apex Systems</v>
       </c>
       <c r="C20" t="str">
-        <v>USD 166,800.00 - 250,000.00</v>
+        <v>USD 67.81 - 72.33</v>
       </c>
       <c r="D20" t="str">
-        <v>White Plains, New York</v>
+        <v>Charlotte, North Carolina</v>
       </c>
       <c r="E20" t="str">
         <v>Today</v>
       </c>
       <c r="F20" t="str">
-        <v>https://www.dice.com/job-detail/68663728-18e1-4d44-9c74-51b3aa900b2b</v>
+        <v>https://www.dice.com/job-detail/e40ad386-88c7-49f7-958e-7aa8797a1f8b</v>
       </c>
       <c r="G20" t="str">
         <v>Data Science</v>
@@ -861,22 +861,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Senior Director, Data Science Product Development, Specialized Risk</v>
+        <v>Senior Manager of Data Science</v>
       </c>
       <c r="B21" t="str">
-        <v>Trans Union LLC</v>
+        <v>Kforce Technology Staffing</v>
       </c>
       <c r="C21" t="str">
-        <v>USD 166,800.00 - 250,000.00</v>
+        <v>$180,000 - $200,000</v>
       </c>
       <c r="D21" t="str">
-        <v>Boca Raton, Florida</v>
+        <v>Louisville, Kentucky</v>
       </c>
       <c r="E21" t="str">
         <v>Today</v>
       </c>
       <c r="F21" t="str">
-        <v>https://www.dice.com/job-detail/99d58368-6f96-4729-aa0f-389e4c851d19</v>
+        <v>https://www.dice.com/job-detail/50935afb-6ec9-4df1-956b-0c24e0301e0f</v>
       </c>
       <c r="G21" t="str">
         <v>Data Science</v>
@@ -884,160 +884,160 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SR FP&amp;A Analyst</v>
+        <v>Technical Program Manager - Marketing Data Science</v>
       </c>
       <c r="B22" t="str">
-        <v>Dexian DISYS</v>
+        <v>Tandym Tech</v>
       </c>
       <c r="C22" t="str">
-        <v>$110</v>
+        <v>$65 - $70</v>
       </c>
       <c r="D22" t="str">
-        <v>Tampa, Florida</v>
+        <v>Vienna, Virginia</v>
       </c>
       <c r="E22" t="str">
         <v>Today</v>
       </c>
       <c r="F22" t="str">
-        <v>https://www.dice.com/job-detail/c8cbc56c-9d36-4dfc-b67f-9785ccc187b5</v>
+        <v>https://www.dice.com/job-detail/880db6de-9ee5-4a3d-a440-ea94fa905c0e</v>
       </c>
       <c r="G22" t="str">
-        <v>FP&amp;A</v>
+        <v>Data Science</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>FP&amp;A Manager</v>
+        <v>Data Science and Analytics</v>
       </c>
       <c r="B23" t="str">
-        <v>Judge Group, Inc.</v>
+        <v>Apex Systems</v>
       </c>
       <c r="C23" t="str">
-        <v>$150,000</v>
+        <v>$60 - $72</v>
       </c>
       <c r="D23" t="str">
-        <v>North Charleston, South Carolina</v>
+        <v>Merrifield, Virginia</v>
       </c>
       <c r="E23" t="str">
         <v>Today</v>
       </c>
       <c r="F23" t="str">
-        <v>https://www.dice.com/job-detail/6a8561f0-d525-45be-aa81-0e4980ca3449</v>
+        <v>https://www.dice.com/job-detail/d3b04d4e-52c7-44c8-ba76-f83c3661a155</v>
       </c>
       <c r="G23" t="str">
-        <v>FP&amp;A</v>
+        <v>Data Science</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>FP&amp;A Director - McKesson Technology</v>
+        <v>Senior Director, Data Science Product Development, Specialized Risk</v>
       </c>
       <c r="B24" t="str">
-        <v>McKesson Corporation</v>
+        <v>Trans Union LLC</v>
       </c>
       <c r="C24" t="str">
-        <v>USD 135,800.00 - 226,400.00</v>
+        <v>USD 166,800.00 - 250,000.00</v>
       </c>
       <c r="D24" t="str">
-        <v>Remote or Irving, Texas</v>
+        <v>New York, New York</v>
       </c>
       <c r="E24" t="str">
         <v>Today</v>
       </c>
       <c r="F24" t="str">
-        <v>https://www.dice.com/job-detail/91d51739-dc79-41f4-80f4-411bb3d5d5b4</v>
+        <v>https://www.dice.com/job-detail/1a3d9e02-ee12-413d-b326-9535e4acb9f0</v>
       </c>
       <c r="G24" t="str">
-        <v>FP&amp;A</v>
+        <v>Data Science</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Senior FP&amp;A Analyst - Technical Infrastructure</v>
+        <v>Senior Director, Data Science Product Development, Specialized Risk</v>
       </c>
       <c r="B25" t="str">
-        <v>Waymo</v>
+        <v>Trans Union LLC</v>
       </c>
       <c r="C25" t="str">
-        <v>USD 168,000.00 - 207,000.00</v>
+        <v>USD 166,800.00 - 250,000.00</v>
       </c>
       <c r="D25" t="str">
-        <v>Mountain View, California</v>
+        <v>Pennsylvania</v>
       </c>
       <c r="E25" t="str">
         <v>Today</v>
       </c>
       <c r="F25" t="str">
-        <v>https://www.dice.com/job-detail/d759580f-5cb2-47fe-9fc7-1dabc1065639</v>
+        <v>https://www.dice.com/job-detail/bb1f8c88-001f-4078-a08a-c548c76b2d8f</v>
       </c>
       <c r="G25" t="str">
-        <v>FP&amp;A</v>
+        <v>Data Science</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>FP&amp;A Analyst</v>
+        <v>Senior Director, Data Science Product Development, Specialized Risk</v>
       </c>
       <c r="B26" t="str">
-        <v>Two Sigma Investments, LLC.</v>
+        <v>Trans Union LLC</v>
       </c>
       <c r="C26" t="str">
-        <v>USD 100,000.00 - 150,000.00</v>
+        <v>USD 166,800.00 - 250,000.00</v>
       </c>
       <c r="D26" t="str">
-        <v>New York, New York</v>
+        <v>Greenwood Village, Colorado</v>
       </c>
       <c r="E26" t="str">
-        <v>2d ago</v>
+        <v>Today</v>
       </c>
       <c r="F26" t="str">
-        <v>https://www.dice.com/job-detail/e381eac2-5e71-4f1c-a14a-c02debed842f</v>
+        <v>https://www.dice.com/job-detail/7b22c851-2330-4460-bcd0-bc4c4c6b638f</v>
       </c>
       <c r="G26" t="str">
-        <v>FP&amp;A</v>
+        <v>Data Science</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>FP&amp;A Data Engineer</v>
+        <v>Senior Director, Data Science Product Development, Specialized Risk</v>
       </c>
       <c r="B27" t="str">
-        <v>Galaxy</v>
+        <v>Trans Union LLC</v>
       </c>
       <c r="C27" t="str">
-        <v>USD 175,000.00 - 200,000.00</v>
+        <v>USD 166,800.00 - 250,000.00</v>
       </c>
       <c r="D27" t="str">
-        <v>New York, New York</v>
+        <v>White Plains, New York</v>
       </c>
       <c r="E27" t="str">
-        <v>4d ago</v>
+        <v>Today</v>
       </c>
       <c r="F27" t="str">
-        <v>https://www.dice.com/job-detail/5aef83cd-6436-4fd9-920a-7b8dca72a25f</v>
+        <v>https://www.dice.com/job-detail/68663728-18e1-4d44-9c74-51b3aa900b2b</v>
       </c>
       <c r="G27" t="str">
-        <v>FP&amp;A</v>
+        <v>Data Science</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Sr Data Analyst - FP&amp;A Reporting &amp; Analytics</v>
+        <v>SR FP&amp;A Analyst</v>
       </c>
       <c r="B28" t="str">
-        <v>Target Corporation</v>
+        <v>Dexian DISYS</v>
       </c>
       <c r="C28" t="str">
-        <v>$88,000</v>
+        <v>$110</v>
       </c>
       <c r="D28" t="str">
-        <v>Remote or Minneapolis, Minnesota</v>
+        <v>Tampa, Florida</v>
       </c>
       <c r="E28" t="str">
         <v>Today</v>
       </c>
       <c r="F28" t="str">
-        <v>https://www.dice.com/job-detail/bf0d9301-c4d4-4f8b-9596-8e997c8cf0fe</v>
+        <v>https://www.dice.com/job-detail/c8cbc56c-9d36-4dfc-b67f-9785ccc187b5</v>
       </c>
       <c r="G28" t="str">
         <v>FP&amp;A</v>
@@ -1045,30 +1045,168 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>SeniorFinanceAnalyst</v>
+        <v>FP&amp;A Manager</v>
       </c>
       <c r="B29" t="str">
-        <v>Infinite Computer Solutions (ICS)</v>
+        <v>Judge Group, Inc.</v>
       </c>
       <c r="C29" t="str">
-        <v>$100,000 - $140,000</v>
+        <v>$150,000</v>
       </c>
       <c r="D29" t="str">
-        <v>Hybrid in Rockville, Maryland</v>
+        <v>North Charleston, South Carolina</v>
       </c>
       <c r="E29" t="str">
-        <v>9d ago</v>
+        <v>Today</v>
       </c>
       <c r="F29" t="str">
-        <v>https://www.dice.com/job-detail/49f3864c-3b4b-4014-b1e7-7886e5b57c0e</v>
+        <v>https://www.dice.com/job-detail/6a8561f0-d525-45be-aa81-0e4980ca3449</v>
       </c>
       <c r="G29" t="str">
         <v>FP&amp;A</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>FP&amp;A Director - McKesson Technology</v>
+      </c>
+      <c r="B30" t="str">
+        <v>McKesson Corporation</v>
+      </c>
+      <c r="C30" t="str">
+        <v>USD 135,800.00 - 226,400.00</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Remote or Irving, Texas</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Today</v>
+      </c>
+      <c r="F30" t="str">
+        <v>https://www.dice.com/job-detail/91d51739-dc79-41f4-80f4-411bb3d5d5b4</v>
+      </c>
+      <c r="G30" t="str">
+        <v>FP&amp;A</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>FP&amp;A Analyst</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Two Sigma Investments, LLC.</v>
+      </c>
+      <c r="C31" t="str">
+        <v>USD 100,000.00 - 150,000.00</v>
+      </c>
+      <c r="D31" t="str">
+        <v>New York, New York</v>
+      </c>
+      <c r="E31" t="str">
+        <v>3d ago</v>
+      </c>
+      <c r="F31" t="str">
+        <v>https://www.dice.com/job-detail/e381eac2-5e71-4f1c-a14a-c02debed842f</v>
+      </c>
+      <c r="G31" t="str">
+        <v>FP&amp;A</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>FP&amp;A Data Engineer</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Galaxy</v>
+      </c>
+      <c r="C32" t="str">
+        <v>USD 175,000.00 - 200,000.00</v>
+      </c>
+      <c r="D32" t="str">
+        <v>New York, New York</v>
+      </c>
+      <c r="E32" t="str">
+        <v>5d ago</v>
+      </c>
+      <c r="F32" t="str">
+        <v>https://www.dice.com/job-detail/5aef83cd-6436-4fd9-920a-7b8dca72a25f</v>
+      </c>
+      <c r="G32" t="str">
+        <v>FP&amp;A</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Sr Data Analyst - FP&amp;A Reporting &amp; Analytics</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Target Corporation</v>
+      </c>
+      <c r="C33" t="str">
+        <v>$88,000</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Remote or Minneapolis, Minnesota</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Today</v>
+      </c>
+      <c r="F33" t="str">
+        <v>https://www.dice.com/job-detail/bf0d9301-c4d4-4f8b-9596-8e997c8cf0fe</v>
+      </c>
+      <c r="G33" t="str">
+        <v>FP&amp;A</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>SeniorFinanceAnalyst</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Infinite Computer Solutions (ICS)</v>
+      </c>
+      <c r="C34" t="str">
+        <v>$100,000 - $140,000</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Hybrid in Rockville, Maryland</v>
+      </c>
+      <c r="E34" t="str">
+        <v>10d ago</v>
+      </c>
+      <c r="F34" t="str">
+        <v>https://www.dice.com/job-detail/49f3864c-3b4b-4014-b1e7-7886e5b57c0e</v>
+      </c>
+      <c r="G34" t="str">
+        <v>FP&amp;A</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Financial Data Analyst</v>
+      </c>
+      <c r="B35" t="str">
+        <v>SSI People</v>
+      </c>
+      <c r="C35" t="str">
+        <v>$40 - $50</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Hybrid in Framingham, Massachusetts</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Today</v>
+      </c>
+      <c r="F35" t="str">
+        <v>https://www.dice.com/job-detail/874f1cc6-cbbb-4bd6-892c-beb6fb07de42</v>
+      </c>
+      <c r="G35" t="str">
+        <v>FP&amp;A</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G35"/>
   </ignoredErrors>
 </worksheet>
 </file>